--- a/data/数据生成策略.xlsx
+++ b/data/数据生成策略.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14980"/>
+    <workbookView windowHeight="14280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
   <si>
     <t>工序</t>
   </si>
@@ -77,9 +77,6 @@
     <t>47-49</t>
   </si>
   <si>
-    <t>这是我根据老师发的和上次的一堆真实数据自己设计的工序和部分参数的取值</t>
-  </si>
-  <si>
     <t>450-500</t>
   </si>
   <si>
@@ -99,6 +96,9 @@
   </si>
   <si>
     <t>加固化剂</t>
+  </si>
+  <si>
+    <t>T1 (83 min)刚加固化剂预测点</t>
   </si>
   <si>
     <t>10～14</t>
@@ -172,7 +172,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[20.0, 30.0]</t>
+      <t>[20.0, 32.0]</t>
     </r>
     <r>
       <rPr>
@@ -197,16 +197,13 @@
     <t>粒径分布参数</t>
   </si>
   <si>
-    <t>这个参数kd应该用不上</t>
-  </si>
-  <si>
     <t>几何标准差</t>
   </si>
   <si>
     <t>σ</t>
   </si>
   <si>
-    <t>[1.4, 1.6]</t>
+    <t>[1.4, 1.9]</t>
   </si>
   <si>
     <t>粒径分布宽度</t>
@@ -245,7 +242,7 @@
     </r>
   </si>
   <si>
-    <t>[0.60, 0.75]</t>
+    <t>[0.63, 0.67]</t>
   </si>
   <si>
     <t>T2 时刻 (111 min) 的固含量</t>
@@ -284,13 +281,10 @@
     </r>
   </si>
   <si>
-    <t>[0.10, 0.25]</t>
+    <t>[0.015, 0.025]</t>
   </si>
   <si>
     <t>固化剂占液相体积的比例，用于反推 T1 时刻固含量</t>
-  </si>
-  <si>
-    <t>Φmax采用下面的策略进行生成、修正，由于这个参数我作为中间变量让模型输出且不参与loss计算，我这边压根没用到，专门给你生成的，你可以看情况重新生成或修正</t>
   </si>
   <si>
     <t>无效数据判定</t>
@@ -489,13 +483,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="8.5"/>
-      <name val="宋体"/>
+      <name val="KaTeX_Math"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -509,12 +509,6 @@
     <font>
       <i/>
       <sz val="13"/>
-      <name val="KaTeX_Math"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8.5"/>
       <name val="KaTeX_Math"/>
       <charset val="134"/>
     </font>
@@ -1069,7 +1063,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1094,9 +1088,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1108,9 +1099,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1402,13 +1390,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>62865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>215900</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1426,7 +1414,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22860" y="4589145"/>
+          <a:off x="22860" y="4802505"/>
           <a:ext cx="4676140" cy="3575685"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1693,7 +1681,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="11.8653846153846" style="1" customWidth="1"/>
@@ -1701,7 +1689,7 @@
     <col min="3" max="3" width="20.7692307692308" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.1538461538462" style="1" customWidth="1"/>
     <col min="5" max="5" width="55.3076923076923" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5865384615385" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.3076923076923" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1800,15 +1788,13 @@
         <v>15</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="H5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="3"/>
@@ -1819,21 +1805,21 @@
         <v>6</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="3"/>
@@ -1841,26 +1827,26 @@
         <v>35</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="5"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1877,215 +1863,217 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="3"/>
-      <c r="B9" s="4">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="5"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="3"/>
       <c r="B10" s="4">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10">
+    <row r="12" spans="1:14">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9">
         <v>15</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="1" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" ht="20" spans="1:14">
-      <c r="A16" s="3" t="s">
+    <row r="17" ht="20" spans="1:14">
+      <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>41</v>
+      <c r="D17" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" ht="17" spans="1:14">
-      <c r="A18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>44</v>
+      <c r="B18" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:14">
       <c r="A19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" ht="17" spans="1:14">
+      <c r="A20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="4" t="s">
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="12" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="13" t="s">
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="14" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="15" t="s">
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="15" t="s">
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A48:E48"/>
     <mergeCell ref="H5:N7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
